--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2474-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2474-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C375B4E5-1AF7-4C37-86E5-482C4F62FD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F05781A1-1FE3-4B44-9F12-04354AE67D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{25321E4E-EB04-41EF-B13A-2D45BC744138}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3FC6D212-DC61-4C6E-9985-20268E04F192}"/>
   </bookViews>
   <sheets>
     <sheet name="2474-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1496,25 +1496,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B798198-2858-4CFC-89C7-32130377EA33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9379203C-38C4-44B9-8360-82CE3FA4149C}">
   <dimension ref="A1:R52"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1542,7 +1542,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1668,7 +1668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2022</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2021</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>25</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2020</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2019</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2018</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2017</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2016</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2015</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2014</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2013</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2012</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2011</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2010</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2009</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2008</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>2007</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2006</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>2005</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2004</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>2003</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>2002</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>2001</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2000</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="37">
         <v>1999</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39">
         <v>1998</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="37">
         <v>1997</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="39">
         <v>1996</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37" t="s">
         <v>51</v>
       </c>
